--- a/human_resources_forms/017_diversity_survey--human_resources_forms.xlsx
+++ b/human_resources_forms/017_diversity_survey--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>How do you feel about the diversity of the company's workforce?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Diversity</t>
+          <t>Which of the following best describes your experiences with equal opportunities at the company?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Equal</t>
+          <t>How often do you feel that your contributions are valued and recognized?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Which of the following best describes your experiences with fair treatment at the company?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,20 +617,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Treat</t>
+          <t>How important do you think diversity and inclusion are to the company's success?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Equally</t>
+          <t>Do you feel that your company promotes diversity and inclusion in the workplace?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>What are the most important reasons you have for not feeling welcome at the company? (Select multiple)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,20 +686,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Survey</t>
+          <t>What are the most important reasons you have for feeling that your contributions are not recognized? (Select multiple)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>How do you feel about the diversity and inclusion initiatives implemented by the company?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Have you ever experienced any form of discrimination or bias in the workplace?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Have you experienced any form of retaliation for reporting or speaking up about diversity and inclusion issues?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,20 +778,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>How confident are you about the company's commitment to diversity and inclusion?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,289 +801,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Would you like to suggest any diversity and inclusion initiatives that the company should implement?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,612 +850,697 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option-1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option-1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option-2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option-2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option-3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option-3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option-4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option-4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option-5</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option-5</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option-6</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option-6</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option-7</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option-7</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option-8</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option-8</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option-9</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option-9</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option-10</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option-10</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option-11</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option-11</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option-12</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option-12</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>page_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option-13</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option-13</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>page_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option-14</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option-14</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option-15</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option-15</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>page_19_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option-17</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option-17</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>page_19_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option-18</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option-18</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>page_19_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option-19</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option-19</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>page_20_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option-20</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option-20</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>page_20_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option-21</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option-21</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>page_20_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option-22</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option-22</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>page_21_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option-23</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option-23</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>page_21_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option-24</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option-24</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>page_21_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option-25</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option-25</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>page_22_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option-26</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option-26</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>page_22_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option-27</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option-27</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>page_22_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option-28</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option-28</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>page_23_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option-29</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option-29</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>page_23_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option-30</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option-30</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>page_23_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option-31</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option-31</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>page_24_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option-32</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option-32</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>page_24_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option-33</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option-33</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>page_24_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option-34</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option-34</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>page_25_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option-35</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option-35</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>page_25_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option-36</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option-36</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>page_25_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option-37</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option-37</t>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>page_12_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>page_12_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>page_12_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>page_13_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>page_13_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
